--- a/medford_lor_oborudovanie.xlsx
+++ b/medford_lor_oborudovanie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Vision, Olympus, Pentax — всего 20 позиций.</t>
+          <t>ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Vision, Olympus, Pentax.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lor_oborudovanie.xlsx
+++ b/medford_lor_oborudovanie.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лОР оборудование для клиники?</t>
+          <t>Что входит в ЛОР-комбайн?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Рабочая длина, мм, Класс). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>ЛОР-комбайн — многофункциональная установка, объединяющая источник света, аспиратор и модули для промывания и распыления лекарств. Часть моделей дооснащается эндоскопией, видеосистемой и нагревом инструментов. Конкретный состав зависит от класса и комплектации; в каталоге есть комбайны Dixion, MEGA MEDICAL и Элема-Н.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Каким приказом регламентировано оснащение ЛОР-кабинета?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Перечень обязательного оборудования для ЛОР-кабинета в России закреплён приказом Минздрава №905н. В него входят ЛОР-комбайн, электрохирургический аппарат, налобный осветитель, отоскоп, риноскоп, аудиометр, негатоскоп, набор камертонов и другие устройства. Комплектацию сверяют с этим нормативом, а на каждое изделие проверяют действующее регистрационное удостоверение.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>С чего начать оснащение кабинета?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены ATMOS, Vision, Olympus, Pentax. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Начинают с анализа потока пациентов и спектра услуг, затем выбирают ЛОР-комбайн как основу рабочего места. К нему добавляют средства визуализации (микроскоп, видеосистему) и диагностические приборы под профиль. Модульные платформы позволяют дооснащать кабинет по мере роста.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Нужны ли регистрационные удостоверения на всё оборудование?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Да. Каждое медицинское изделие в ЛОР-кабинете должно иметь действующее регистрационное удостоверение Росздравнадзора — это условие легального применения и лицензирования. Наличие и реквизиты РУ на каждую позицию уточняйте до покупки; без РУ изделие нельзя использовать в лицензируемой деятельности, даже если оно исправно.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Можно ли дооснастить оборудование позже?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Многие ЛОР-комбайны и видеостойки модульные: к базе добавляют эндоскопию, видеозапись, дополнительные каналы и инструменты по мере расширения услуг. При выборе платформы уточните перечень доступных опций, чтобы не менять основу при развитии клиники. Это позволяет распределить вложения и наращивать функции постепенно.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какие инструменты использует лор-врач?</t>
+          <t>Совместима ли ЛОР-камера с моими эндоскопами?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>ЛОР-видеосистемы и камеры (Chammed, MEDSTAR, ATMOS) рассчитаны на работу с жёсткими и гибкими эндоскопами через соответствующий адаптер. Совместимость зависит от типа эндоскопа, коннектора и монитора — сообщите имеющееся оборудование, и мы сверим подключение до поставки.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Что должно быть в лор кабинете?</t>
+          <t>Предоставляете ли сервис на ЛОР-оборудование?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>На поставляемое оборудование распространяется гарантия, а обслуживание и ремонт комбайнов, микроскопов и видеосистем выполняет собственный инженерный сервис. Условия, срок гарантии и порядок обращения по конкретной позиции уточняйте у менеджера. Для комбайнов отдельно оговаривают обслуживание аспирационных и промывочных модулей, требующих регулярного ухода.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Vision, Olympus, Pentax.</t>
+          <t>ЛОР-оборудование — это комплекс приборов для диагностики и лечения заболеваний уха, горла и носа. В каталоге собраны ЛОР-комбайны (Dixion ST-E500, MEGA MEDICAL NET-1100, Элема-Н ЛК1), диагностические микроскопы (Chammed OMS-2350, ATMOS i View 21 и 31), видеосистемы и ЛОР-камеры (Chammed QVION 15, MEDSTAR MedVision, ATMOS Cam 31), стробоскопы, эхосинускопы (Oriola Sinuscan-201), аспираторы и видеоназофарингоскопы. Оснащение ЛОР-кабинета в России регламентировано приказом Минздрава №905н.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Категории ЛОР-оборудования по назначению</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР оборудование</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4402,235 +4402,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Категории ЛОР-оборудования по назначению</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Категория</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Примеры приборов</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Класс</t>
+          <t>Пример моделей каталога</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Микроскоп оториноларингологический Chammed OMS-2350</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Диагностическое</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Микроскопы, эндоскопы, эхосинускопы, ЛОР-камеры</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Южная Корея</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>67308</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Chammed OMS-2350, Oriola Sinuscan-201, ATMOS Cam 31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Эхосинускоп Oriola Sinuscan-201</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Хирургическое</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ЛОР-комбайны, микроскопы, электрохирургия</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Финляндия</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>67434</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Dixion ST-E500, MEGA MEDICAL NET-1100, Элема-Н ЛК1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-установка Dixion ST-E500</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Визуализация</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Видеосистемы, стробоскопы, назофарингоскопы</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Средний</t>
+          <t>Chammed QVION 15, ATMOS Strobo 21, Pentax VNL9-CP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Стробоскоп ATMOS Strobo 21 LED</t>
+          <t>Вспомогательное</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ATMOS</t>
+          <t>Аспираторы, осветители</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ЛОР-камера ATMOS Cam 31</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>ATMOS</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Процедурный ЛОР-аппарат Trima ИНТРА-ЛОР</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ATMOS C 161</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4642,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4968,12 +4842,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите профиль и поток кабинета</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лОР оборудование: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Состав оборудования зависит от задач: для базовой поликлиники хватит ЛОР-комбайна и диагностического набора, для специализированного центра нужны микроскоп, видеосистема, стробоскоп и эндоскопы. Оцените поток пациентов и спектр услуг — это задаёт класс комбайна и глубину оснащения.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5013,12 +4887,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите ЛОР-комбайн как основу</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>ЛОР-комбайн объединяет источник света, аспирацию и модули промывания и распыления. В каталоге есть модели среднего класса Dixion ST-E500 и MEGA MEDICAL NET-1100, отечественная Элема-Н ЛК1 с автоклавируемыми банками и ёмкостью 3 л. Ориентируйтесь на набор модулей и материал корпуса.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5058,12 +4932,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Добавьте средства визуализации</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Рабочая длина, мм, Класс. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Для осмотра и операций выбирают микроскоп (Chammed OMS-2350, ATMOS i View 21/31) и ЛОР-видеосистему (Chammed QVION 15 HD, MEDSTAR MedVision, ATMOS Cam 31). Видеосистема с эндоскопом даёт картинку на монитор и документирование. Сверьте разрешение камеры и совместимость с эндоскопами.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5103,12 +4977,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Подберите диагностические приборы</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: ATMOS, Vision, Olympus, Pentax.</t>
+          <t>Под задачи добавляют эхосинускоп для УЗ-исследования пазух (Oriola Sinuscan-201), стробоскоп для оценки голосовых складок (ATMOS Strobo 21 LED), видеоназофарингоскопы (Pentax VNL9-CP, Otopront Chip-on-the-Tip) и аспиратор (ATMOS C 161). Набор формируют по спектру приёма.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5148,12 +5022,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Заложите модульность и расширение</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Многие комбайны и стойки дооснащаются модулями по мере роста услуг. Выбирайте платформу, к которой можно добавить эндоскопию, видеозапись или дополнительные каналы, чтобы не менять базу при расширении. Уточните перечень доступных опций у конкретной модели.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5193,12 +5067,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Сверьте регистрацию и стандарты оснащения</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Всё оборудование должно иметь действующие регистрационные удостоверения Росздравнадзора, иначе его нельзя применять в лицензируемой деятельности. Состав обязательного оснащения ЛОР-кабинета в России закреплён приказом Минздрава №905н. Сверьте комплектацию с нормативом и запросите РУ на каждую позицию до покупки, чтобы избежать проблем при лицензировании.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5248,7 +5122,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ЛОР оборудование подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены ATMOS, Vision, Olympus, Pentax. При выборе обращают внимание на страна производства, производитель, рабочая длина, класс, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Оснащение ЛОР-кабинета я советую начинать с ЛОР-комбайна — это центр рабочего места, к нему уже добавляют микроскоп, видеосистему и эндоскопы под спектр услуг. Модульность важна: многие установки дооснащаются по мере роста клиники, поэтому лучше сразу заложить возможность расширения. Обязательно проверяю действующие регистрационные удостоверения на каждую позицию и соответствие приказу №905н. Совместимость видеокамеры с эндоскопом и монитором сверяю до поставки.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5532,13 +5406,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР оборудование</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ЛОР оборудование — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов ATMOS, Vision, Olympus, Pentax. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-оборудование объединяет приборы для диагностики и лечения болезней уха, горла и носа. По назначению его делят на диагностическое (микроскопы, эндоскопы, эхосинускопы, ЛОР-камеры), хирургическое (ЛОР-комбайны, микроскопы, электрохирургия), терапевтическое и вспомогательное. Основа кабинета — ЛОР-комбайн, объединяющий источник света, аспирацию и модули промывания и распыления. В каталоге представлены комбайны Dixion, MEGA MEDICAL и Элема-Н, микроскопы и видеосистемы Chammed и ATMOS. Состав оснащения ЛОР-кабинета в России регламентирует приказ Минздрава №905н, а всё оборудование требует действующего РУ Росздравнадзора.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5575,13 +5449,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что относят к ЛОР-оборудованию</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Рабочая длина, мм, Класс), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>ЛОР-оборудование — комплекс приборов, которые оториноларинголог использует для диагностики, лечения и профилактики болезней уха, горла и носа. Сюда входят ЛОР-комбайны, микроскопы, эндоскопы и видеосистемы, стробоскопы, эхосинускопы, аспираторы и осветители. От точности и функциональности приборов зависят эффективность приёма и комфорт пациента.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5618,13 +5492,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Классификация по назначению</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По назначению оборудование делят на диагностическое (отоскопы, риноскопы, эндоскопы, аудиометры, эхосинускопы, ЛОР-камеры), хирургическое (ЛОР-комбайны, микроскопы, электрохирургические аппараты, лазеры), терапевтическое (небулайзеры, ингаляторы) и вспомогательное (налобные осветители, лупы, инструменты). Такое деление помогает формировать комплектацию под профиль кабинета.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5661,13 +5535,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>ЛОР-комбайн как основа кабинета</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>ЛОР-комбайн — центр рабочего места врача: он объединяет источник света, аспирацию и модули промывания и распыления. В каталоге представлены комбайны среднего класса Dixion ST-E500 и MEGA MEDICAL NET-1100, а также отечественная Элема-Н ЛК1 с автоклавируемыми аспирационными банками. Модульность позволяет дооснащать установку.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5684,6 +5558,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Требования и стандарты</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Состав обязательного оснащения ЛОР-кабинета в России закреплён приказом Минздрава №905н. Всё оборудование должно иметь действующие регистрационные удостоверения Росздравнадзора, иначе его нельзя применять в лицензируемой деятельности. При комплектации кабинета проверяют соответствие нормативу и наличие РУ на каждую позицию.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lor_oborudovanie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
